--- a/education_forms/039_educator_course_material_upload_form--education_forms.xlsx
+++ b/education_forms/039_educator_course_material_upload_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,8 +1056,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'beginner',_'label':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Beginner', 'label': 'Beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'intermediate',_'label':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Intermediate', 'label': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'advanced',_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Advanced', 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'beginner',_'label':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Beginner', 'label': 'Beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'intermediate',_'label':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Intermediate', 'label': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'advanced',_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Advanced', 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
